--- a/Summer2022-2025-DataAnalysis/RawData/Zoop_sample_counting_template_2022-2025.xlsx
+++ b/Summer2022-2025-DataAnalysis/RawData/Zoop_sample_counting_template_2022-2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/heatherwander/Documents/VirginiaTech/research/zooplankton/Summer2022-2025-DataAnalysis/RawData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0D2F52-16E9-0E47-89D4-9F4309FC3199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5EE656F-41C1-1249-A0EA-01AB4CCD0B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15900" xr2:uid="{3D67C25D-D874-DE45-AEE3-7A59E1B23F3C}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="28">
   <si>
     <t>Sample_ID</t>
   </si>
@@ -90,37 +90,34 @@
     <t>Cyc naup</t>
   </si>
   <si>
+    <t>Keratella</t>
+  </si>
+  <si>
+    <t>K. bostoniensis</t>
+  </si>
+  <si>
+    <t>Conochilus</t>
+  </si>
+  <si>
     <t>Cal naup</t>
   </si>
   <si>
-    <t>Keratella</t>
+    <t>1 mL</t>
   </si>
   <si>
-    <t>Calanoida</t>
+    <t>B22Jul24_10m</t>
   </si>
   <si>
-    <t>Daphnia</t>
+    <t>Ceriodaphnia</t>
+  </si>
+  <si>
+    <t>Asplanchna</t>
   </si>
   <si>
     <t>B. longirostris</t>
   </si>
   <si>
-    <t>B04Dec23_9m</t>
-  </si>
-  <si>
-    <t>2 mL</t>
-  </si>
-  <si>
-    <t>Gastropus</t>
-  </si>
-  <si>
-    <t>Polyarthra</t>
-  </si>
-  <si>
-    <t>Lecane</t>
-  </si>
-  <si>
-    <t>Ascomorpha</t>
+    <t>Conochiloides</t>
   </si>
 </sst>
 </file>
@@ -521,7 +518,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D676C963-F956-4A49-8829-4831A47E6094}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:XFD1048576"/>
+  <dimension ref="A1:XFD1048574"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -546,7 +543,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2">
-        <v>45264</v>
+        <v>45495</v>
       </c>
       <c r="C2"/>
     </row>
@@ -555,7 +552,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>45800</v>
+        <v>45814</v>
       </c>
       <c r="C3"/>
     </row>
@@ -565,7 +562,7 @@
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -599,13 +596,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>14</v>
@@ -613,21 +610,19 @@
       <c r="E7" s="3">
         <v>1000</v>
       </c>
-      <c r="F7" s="3">
-        <v>1</v>
-      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="6"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>14</v>
@@ -635,21 +630,19 @@
       <c r="E8" s="3">
         <v>1000</v>
       </c>
-      <c r="F8" s="3">
-        <v>0.7</v>
-      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="6"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>14</v>
@@ -657,21 +650,19 @@
       <c r="E9" s="3">
         <v>1000</v>
       </c>
-      <c r="F9" s="3">
-        <v>1</v>
-      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>14</v>
@@ -685,13 +676,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>14</v>
@@ -699,21 +690,19 @@
       <c r="E11" s="3">
         <v>1000</v>
       </c>
-      <c r="F11" s="3">
-        <v>1</v>
-      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12">
-        <v>1.1000000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>14</v>
@@ -721,21 +710,19 @@
       <c r="E12" s="3">
         <v>1000</v>
       </c>
-      <c r="F12" s="3">
-        <v>0.9</v>
-      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13">
-        <v>1.2</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>14</v>
@@ -743,21 +730,19 @@
       <c r="E13" s="3">
         <v>1000</v>
       </c>
-      <c r="F13" s="3">
-        <v>0.9</v>
-      </c>
+      <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14">
-        <v>1.1000000000000001</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>14</v>
@@ -765,21 +750,19 @@
       <c r="E14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3">
-        <v>0.9</v>
-      </c>
+      <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>14</v>
@@ -787,21 +770,19 @@
       <c r="E15" s="3">
         <v>1000</v>
       </c>
-      <c r="F15" s="3">
-        <v>1</v>
-      </c>
+      <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
       </c>
       <c r="C16">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>14</v>
@@ -809,21 +790,19 @@
       <c r="E16" s="3">
         <v>1000</v>
       </c>
-      <c r="F16" s="3">
-        <v>0.9</v>
-      </c>
+      <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>27</v>
+      <c r="A17" t="s">
+        <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
       <c r="C17">
-        <v>1.2</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>14</v>
@@ -831,21 +810,19 @@
       <c r="E17" s="3">
         <v>1000</v>
       </c>
-      <c r="F17" s="3">
-        <v>0.9</v>
-      </c>
+      <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
       </c>
       <c r="C18">
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>14</v>
@@ -853,21 +830,19 @@
       <c r="E18" s="3">
         <v>1000</v>
       </c>
-      <c r="F18" s="3">
-        <v>0.9</v>
-      </c>
+      <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
       </c>
       <c r="C19">
-        <v>1.1000000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>14</v>
@@ -875,21 +850,19 @@
       <c r="E19" s="3">
         <v>1000</v>
       </c>
-      <c r="F19" s="3">
-        <v>0.9</v>
-      </c>
+      <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
       </c>
       <c r="C20">
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>14</v>
@@ -897,21 +870,19 @@
       <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3">
-        <v>0.9</v>
-      </c>
+      <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
       </c>
       <c r="C21">
-        <v>1.1000000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>14</v>
@@ -919,21 +890,19 @@
       <c r="E21" s="3">
         <v>1000</v>
       </c>
-      <c r="F21" s="3">
-        <v>0.9</v>
-      </c>
+      <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="6"/>
+      <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B22" t="s">
         <v>12</v>
       </c>
       <c r="C22">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>14</v>
@@ -941,21 +910,19 @@
       <c r="E22" s="3">
         <v>1000</v>
       </c>
-      <c r="F22" s="3">
-        <v>0.9</v>
-      </c>
+      <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="H22" s="6"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
       </c>
       <c r="C23">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>14</v>
@@ -963,21 +930,19 @@
       <c r="E23" s="3">
         <v>1000</v>
       </c>
-      <c r="F23" s="3">
-        <v>1</v>
-      </c>
+      <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="6"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>14</v>
@@ -985,9 +950,7 @@
       <c r="E24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
-        <v>0.8</v>
-      </c>
+      <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="6"/>
     </row>
@@ -1008,20 +971,20 @@
         <v>1000</v>
       </c>
       <c r="F25" s="3">
-        <v>1.1000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="6"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
       </c>
       <c r="C26">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>14</v>
@@ -1029,19 +992,21 @@
       <c r="E26" s="3">
         <v>1000</v>
       </c>
-      <c r="F26" s="3"/>
+      <c r="F26" s="3">
+        <v>0.5</v>
+      </c>
       <c r="G26" s="3"/>
       <c r="H26" s="6"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B27" t="s">
         <v>12</v>
       </c>
       <c r="C27">
-        <v>4.5999999999999996</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>14</v>
@@ -1055,9 +1020,14 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28"/>
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28">
+        <v>4.4000000000000004</v>
+      </c>
       <c r="D28" s="8" t="s">
         <v>14</v>
       </c>
@@ -1070,9 +1040,14 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29"/>
+        <v>24</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29">
+        <v>6</v>
+      </c>
       <c r="D29" s="8" t="s">
         <v>14</v>
       </c>
@@ -1085,9 +1060,14 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30"/>
+        <v>17</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30">
+        <v>1.7</v>
+      </c>
       <c r="D30" s="8" t="s">
         <v>14</v>
       </c>
@@ -1096,17 +1076,17 @@
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="6"/>
+      <c r="H30" s="3"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
       </c>
       <c r="C31">
-        <v>1.1000000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>14</v>
@@ -1114,21 +1094,19 @@
       <c r="E31" s="3">
         <v>1000</v>
       </c>
-      <c r="F31" s="3">
-        <v>0.8</v>
-      </c>
+      <c r="F31" s="3"/>
       <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
+      <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
       </c>
       <c r="C32">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>14</v>
@@ -1142,28 +1120,35 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C33"/>
+        <v>20</v>
+      </c>
+      <c r="B33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
       <c r="D33" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="3">
         <v>1000</v>
       </c>
-      <c r="F33" s="3"/>
+      <c r="F33" s="3">
+        <v>0.5</v>
+      </c>
       <c r="G33" s="3"/>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
       </c>
       <c r="C34">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>14</v>
@@ -1171,22 +1156,17 @@
       <c r="E34" s="3">
         <v>1000</v>
       </c>
-      <c r="F34" s="3">
-        <v>1</v>
-      </c>
-      <c r="G34" s="3"/>
+      <c r="F34" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="G34" s="4"/>
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35">
-        <v>3.9</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C35"/>
       <c r="D35" s="8" t="s">
         <v>14</v>
       </c>
@@ -1199,7 +1179,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C36"/>
       <c r="D36" s="8" t="s">
@@ -1214,7 +1194,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C37"/>
       <c r="D37" s="8" t="s">
@@ -1229,7 +1209,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C38"/>
       <c r="D38" s="8" t="s">
@@ -1244,14 +1224,9 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39">
-        <v>3.4</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C39"/>
       <c r="D39" s="8" t="s">
         <v>14</v>
       </c>
@@ -1259,19 +1234,14 @@
         <v>1000</v>
       </c>
       <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="6"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40">
-        <v>1.9</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C40"/>
       <c r="D40" s="8" t="s">
         <v>14</v>
       </c>
@@ -1280,31 +1250,26 @@
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
+      <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B41" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41">
-        <v>6.5</v>
-      </c>
+      <c r="C41"/>
       <c r="D41" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E41" s="3">
         <v>1000</v>
       </c>
-      <c r="F41" s="4"/>
+      <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C42"/>
       <c r="D42" s="8" t="s">
@@ -1315,11 +1280,10 @@
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
-      <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C43"/>
       <c r="D43" s="8" t="s">
@@ -1330,10 +1294,11 @@
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
+      <c r="H43" s="6"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C44"/>
       <c r="D44" s="8" t="s">
@@ -1348,95 +1313,67 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B45" t="s">
-        <v>12</v>
-      </c>
-      <c r="C45">
-        <v>1.3</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C45"/>
       <c r="D45" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3">
-        <v>1.1000000000000001</v>
-      </c>
+      <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="6"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C46">
-        <v>1.1000000000000001</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C46"/>
       <c r="D46" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E46" s="3">
         <v>1000</v>
       </c>
-      <c r="F46" s="3">
-        <v>0.8</v>
-      </c>
+      <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="6"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B47" t="s">
-        <v>12</v>
-      </c>
-      <c r="C47">
-        <v>1.9</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C47"/>
       <c r="D47" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E47" s="3">
         <v>1000</v>
       </c>
-      <c r="F47" s="3">
-        <v>1.4</v>
-      </c>
+      <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="6"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B48" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48">
-        <v>1.2</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C48"/>
       <c r="D48" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E48" s="3">
         <v>1000</v>
       </c>
-      <c r="F48" s="3">
-        <v>0.9</v>
-      </c>
+      <c r="F48" s="3"/>
       <c r="G48" s="3"/>
-      <c r="H48" s="6"/>
+      <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C49"/>
       <c r="D49" s="8" t="s">
@@ -1448,10 +1385,11 @@
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="4"/>
+      <c r="XFD49" s="6"/>
     </row>
     <row r="50" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C50"/>
       <c r="D50" s="8" t="s">
@@ -1462,19 +1400,13 @@
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
-      <c r="H50" s="4"/>
-      <c r="XFD50" s="6"/>
+      <c r="H50" s="6"/>
     </row>
     <row r="51" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B51" t="s">
-        <v>12</v>
-      </c>
-      <c r="C51">
-        <v>1.5</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C51"/>
       <c r="D51" s="8" t="s">
         <v>14</v>
       </c>
@@ -1487,14 +1419,9 @@
     </row>
     <row r="52" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B52" t="s">
-        <v>12</v>
-      </c>
-      <c r="C52">
-        <v>2.6</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C52"/>
       <c r="D52" s="8" t="s">
         <v>14</v>
       </c>
@@ -1507,29 +1434,22 @@
     </row>
     <row r="53" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B53" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53">
-        <v>1.1000000000000001</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C53"/>
       <c r="D53" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E53" s="3">
         <v>1000</v>
       </c>
-      <c r="F53" s="3">
-        <v>0.7</v>
-      </c>
+      <c r="F53" s="3"/>
       <c r="G53" s="3"/>
-      <c r="H53" s="6"/>
+      <c r="H53" s="4"/>
     </row>
     <row r="54" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C54"/>
       <c r="D54" s="8" t="s">
@@ -1540,18 +1460,13 @@
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
-      <c r="H54" s="4"/>
+      <c r="H54" s="6"/>
     </row>
     <row r="55" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B55" t="s">
-        <v>12</v>
-      </c>
-      <c r="C55">
-        <v>3.3</v>
-      </c>
+      <c r="C55"/>
       <c r="D55" s="8" t="s">
         <v>14</v>
       </c>
@@ -1564,36 +1479,24 @@
     </row>
     <row r="56" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B56" t="s">
-        <v>12</v>
-      </c>
-      <c r="C56">
-        <v>1.4</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C56"/>
       <c r="D56" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E56" s="3">
         <v>1000</v>
       </c>
-      <c r="F56" s="3">
-        <v>1</v>
-      </c>
+      <c r="F56" s="3"/>
       <c r="G56" s="3"/>
       <c r="H56" s="6"/>
     </row>
     <row r="57" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B57" t="s">
-        <v>12</v>
-      </c>
-      <c r="C57">
-        <v>3.7</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C57"/>
       <c r="D57" s="8" t="s">
         <v>14</v>
       </c>
@@ -1608,12 +1511,7 @@
       <c r="A58" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B58" t="s">
-        <v>12</v>
-      </c>
-      <c r="C58">
-        <v>3.3</v>
-      </c>
+      <c r="C58"/>
       <c r="D58" s="8" t="s">
         <v>14</v>
       </c>
@@ -1626,7 +1524,7 @@
     </row>
     <row r="59" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C59"/>
       <c r="D59" s="8" t="s">
@@ -1641,14 +1539,9 @@
     </row>
     <row r="60" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>12</v>
-      </c>
-      <c r="C60">
-        <v>3</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C60"/>
       <c r="D60" s="8" t="s">
         <v>14</v>
       </c>
@@ -1661,29 +1554,22 @@
     </row>
     <row r="61" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B61" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61">
-        <v>1.1000000000000001</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C61"/>
       <c r="D61" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E61" s="3">
         <v>1000</v>
       </c>
-      <c r="F61" s="3">
-        <v>1.1000000000000001</v>
-      </c>
+      <c r="F61" s="3"/>
       <c r="G61" s="3"/>
       <c r="H61" s="6"/>
     </row>
     <row r="62" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C62"/>
       <c r="D62" s="8" t="s">
@@ -1698,7 +1584,7 @@
     </row>
     <row r="63" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C63"/>
       <c r="D63" s="8" t="s">
@@ -1713,13 +1599,13 @@
     </row>
     <row r="64" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B64" t="s">
         <v>12</v>
       </c>
       <c r="C64">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>14</v>
@@ -1733,13 +1619,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B65" t="s">
         <v>12</v>
       </c>
       <c r="C65">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>14</v>
@@ -1755,9 +1641,14 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C66"/>
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66">
+        <v>2.2999999999999998</v>
+      </c>
       <c r="D66" s="8" t="s">
         <v>14</v>
       </c>
@@ -1770,13 +1661,13 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B67" t="s">
         <v>12</v>
       </c>
       <c r="C67">
-        <v>1.1000000000000001</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>14</v>
@@ -1784,17 +1675,20 @@
       <c r="E67" s="3">
         <v>1000</v>
       </c>
-      <c r="F67" s="3">
-        <v>0.8</v>
-      </c>
+      <c r="F67" s="3"/>
       <c r="G67" s="3"/>
       <c r="H67" s="6"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C68"/>
+        <v>21</v>
+      </c>
+      <c r="B68" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68">
+        <v>1.8</v>
+      </c>
       <c r="D68" s="8" t="s">
         <v>14</v>
       </c>
@@ -1804,12 +1698,18 @@
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
       <c r="H68" s="6"/>
+      <c r="I68" s="6"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C69"/>
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69">
+        <v>2</v>
+      </c>
       <c r="D69" s="8" t="s">
         <v>14</v>
       </c>
@@ -1819,17 +1719,16 @@
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
       <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B70" t="s">
         <v>12</v>
       </c>
       <c r="C70">
-        <v>7</v>
+        <v>1.6</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>14</v>
@@ -1839,17 +1738,17 @@
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
-      <c r="H70" s="6"/>
+      <c r="H70" s="4"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B71" t="s">
         <v>12</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>14</v>
@@ -1857,21 +1756,19 @@
       <c r="E71" s="3">
         <v>1000</v>
       </c>
-      <c r="F71" s="3">
-        <v>0.7</v>
-      </c>
+      <c r="F71" s="3"/>
       <c r="G71" s="3"/>
-      <c r="H71" s="4"/>
+      <c r="H71" s="6"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
         <v>12</v>
       </c>
       <c r="C72">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>14</v>
@@ -1879,9 +1776,7 @@
       <c r="E72" s="3">
         <v>1000</v>
       </c>
-      <c r="F72" s="3">
-        <v>0.7</v>
-      </c>
+      <c r="F72" s="3"/>
       <c r="G72" s="3"/>
       <c r="H72" s="6"/>
     </row>
@@ -1889,14 +1784,21 @@
       <c r="A73" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C73"/>
+      <c r="B73" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73">
+        <v>1.4</v>
+      </c>
       <c r="D73" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E73" s="3">
         <v>1000</v>
       </c>
-      <c r="F73" s="3"/>
+      <c r="F73" s="3">
+        <v>1.3</v>
+      </c>
       <c r="G73" s="3"/>
       <c r="H73" s="6"/>
     </row>
@@ -1908,7 +1810,7 @@
         <v>12</v>
       </c>
       <c r="C74">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>14</v>
@@ -1922,9 +1824,14 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C75"/>
+        <v>17</v>
+      </c>
+      <c r="B75" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75">
+        <v>1.4</v>
+      </c>
       <c r="D75" s="8" t="s">
         <v>14</v>
       </c>
@@ -1937,9 +1844,14 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C76"/>
+        <v>17</v>
+      </c>
+      <c r="B76" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
       <c r="D76" s="8" t="s">
         <v>14</v>
       </c>
@@ -1952,9 +1864,14 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C77"/>
+        <v>24</v>
+      </c>
+      <c r="B77" t="s">
+        <v>12</v>
+      </c>
+      <c r="C77">
+        <v>5.2</v>
+      </c>
       <c r="D77" s="8" t="s">
         <v>14</v>
       </c>
@@ -1963,17 +1880,17 @@
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
-      <c r="H77" s="6"/>
+      <c r="H77" s="4"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B78" t="s">
         <v>12</v>
       </c>
       <c r="C78">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>14</v>
@@ -1981,21 +1898,19 @@
       <c r="E78" s="3">
         <v>1000</v>
       </c>
-      <c r="F78" s="3">
-        <v>0.7</v>
-      </c>
+      <c r="F78" s="3"/>
       <c r="G78" s="3"/>
-      <c r="H78" s="4"/>
+      <c r="H78" s="6"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B79" t="s">
         <v>12</v>
       </c>
       <c r="C79">
-        <v>2.9</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>14</v>
@@ -2004,32 +1919,24 @@
         <v>1000</v>
       </c>
       <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="6"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B80" t="s">
-        <v>12</v>
-      </c>
-      <c r="C80">
-        <v>1.2</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C80"/>
       <c r="D80" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E80" s="3">
         <v>1000</v>
       </c>
-      <c r="F80" s="3">
-        <v>1.2</v>
-      </c>
+      <c r="F80" s="3"/>
+      <c r="H80" s="3"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C81"/>
       <c r="D81" s="8" t="s">
@@ -2039,13 +1946,19 @@
         <v>1000</v>
       </c>
       <c r="F81" s="3"/>
-      <c r="H81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="4"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C82"/>
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82">
+        <v>2.1</v>
+      </c>
       <c r="D82" s="8" t="s">
         <v>14</v>
       </c>
@@ -2054,18 +1967,13 @@
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
-      <c r="H82" s="4"/>
+      <c r="H82" s="5"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B83" t="s">
-        <v>12</v>
-      </c>
-      <c r="C83">
-        <v>2.7</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C83"/>
       <c r="D83" s="8" t="s">
         <v>14</v>
       </c>
@@ -2073,12 +1981,12 @@
         <v>1000</v>
       </c>
       <c r="F83" s="3"/>
-      <c r="G83" s="3"/>
-      <c r="H83" s="5"/>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C84"/>
       <c r="D84" s="8" t="s">
@@ -2088,12 +1996,12 @@
         <v>1000</v>
       </c>
       <c r="F84" s="3"/>
-      <c r="G84" s="6"/>
+      <c r="G84" s="3"/>
       <c r="H84" s="6"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C85"/>
       <c r="D85" s="8" t="s">
@@ -2108,35 +2016,28 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B86" t="s">
-        <v>12</v>
-      </c>
-      <c r="C86">
-        <v>1.2</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C86"/>
       <c r="D86" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E86" s="3">
         <v>1000</v>
       </c>
-      <c r="F86" s="3">
-        <v>0.8</v>
-      </c>
+      <c r="F86" s="3"/>
       <c r="G86" s="3"/>
       <c r="H86" s="6"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B87" t="s">
         <v>12</v>
       </c>
       <c r="C87">
-        <v>2.8</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>14</v>
@@ -2150,9 +2051,14 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C88"/>
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>12</v>
+      </c>
+      <c r="C88">
+        <v>3.2</v>
+      </c>
       <c r="D88" s="8" t="s">
         <v>14</v>
       </c>
@@ -2161,70 +2067,72 @@
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
-      <c r="H88" s="6"/>
+      <c r="H88" s="4"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C89"/>
+        <v>27</v>
+      </c>
+      <c r="B89" t="s">
+        <v>12</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
       <c r="D89" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E89" s="3">
         <v>1000</v>
       </c>
-      <c r="F89" s="3"/>
+      <c r="F89" s="3">
+        <v>0.7</v>
+      </c>
       <c r="G89" s="3"/>
-      <c r="H89" s="4"/>
+      <c r="H89" s="6"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C90"/>
+        <v>27</v>
+      </c>
+      <c r="B90" t="s">
+        <v>12</v>
+      </c>
+      <c r="C90">
+        <v>1.2</v>
+      </c>
       <c r="D90" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E90" s="3">
         <v>1000</v>
       </c>
-      <c r="F90" s="3"/>
+      <c r="F90" s="3">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="G90" s="3"/>
       <c r="H90" s="6"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B91" t="s">
-        <v>12</v>
-      </c>
-      <c r="C91">
-        <v>1.2</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C91"/>
       <c r="D91" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E91" s="3">
         <v>1000</v>
       </c>
-      <c r="F91" s="3">
-        <v>0.8</v>
-      </c>
+      <c r="F91" s="3"/>
       <c r="G91" s="3"/>
       <c r="H91" s="6"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B92" t="s">
-        <v>12</v>
-      </c>
-      <c r="C92">
-        <v>8.1</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C92"/>
       <c r="D92" s="8" t="s">
         <v>14</v>
       </c>
@@ -2237,13 +2145,13 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B93" t="s">
         <v>12</v>
       </c>
       <c r="C93">
-        <v>1.1000000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="D93" s="8" t="s">
         <v>14</v>
@@ -2251,21 +2159,19 @@
       <c r="E93" s="3">
         <v>1000</v>
       </c>
-      <c r="F93" s="3">
-        <v>0.7</v>
-      </c>
+      <c r="F93" s="3"/>
       <c r="G93" s="3"/>
       <c r="H93" s="6"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B94" t="s">
         <v>12</v>
       </c>
-      <c r="C94">
-        <v>4.7</v>
+      <c r="C94" s="10">
+        <v>1</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>14</v>
@@ -2273,13 +2179,15 @@
       <c r="E94" s="3">
         <v>1000</v>
       </c>
-      <c r="F94" s="3"/>
+      <c r="F94" s="3">
+        <v>0.8</v>
+      </c>
       <c r="G94" s="3"/>
       <c r="H94" s="6"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B95" s="3"/>
       <c r="C95" s="10"/>
@@ -2291,11 +2199,11 @@
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
-      <c r="H95" s="6"/>
+      <c r="H95" s="4"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B96" s="3"/>
       <c r="C96" s="10"/>
@@ -2307,17 +2215,17 @@
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
-      <c r="H96" s="4"/>
+      <c r="H96" s="6"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C97" s="10">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>14</v>
@@ -2325,20 +2233,22 @@
       <c r="E97" s="3">
         <v>1000</v>
       </c>
-      <c r="F97" s="3">
-        <v>1.1000000000000001</v>
-      </c>
+      <c r="F97" s="3"/>
       <c r="G97" s="3"/>
       <c r="H97" s="6"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B98" s="3"/>
-      <c r="C98" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C98" s="10">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="D98" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E98" s="3">
         <v>1000</v>
@@ -2349,115 +2259,114 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C99" s="10">
-        <v>2.9</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B99" s="3"/>
+      <c r="C99" s="10"/>
       <c r="D99" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E99" s="3">
         <v>1000</v>
       </c>
-      <c r="F99" s="3"/>
       <c r="G99" s="3"/>
       <c r="H99" s="6"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B100" s="3"/>
       <c r="C100" s="10"/>
       <c r="D100" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E100" s="3">
         <v>1000</v>
       </c>
+      <c r="F100" s="3"/>
       <c r="G100" s="3"/>
       <c r="H100" s="6"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C101" s="5">
-        <v>1.2</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B101" s="3"/>
       <c r="D101" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E101" s="3">
         <v>1000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>1.1000000000000001</v>
       </c>
       <c r="G101" s="3"/>
       <c r="H101" s="6"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B102" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C102" s="5">
+        <v>1.8</v>
+      </c>
       <c r="D102" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E102" s="3">
         <v>1000</v>
       </c>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3"/>
+      <c r="F102">
+        <v>0.9</v>
+      </c>
       <c r="H102" s="6"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C103" s="5">
-        <v>2.4</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B103" s="3"/>
       <c r="D103" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E103" s="3">
         <v>1000</v>
       </c>
+      <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="6"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B104" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C104" s="5">
+        <v>2</v>
+      </c>
       <c r="D104" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E104" s="3">
         <v>1000</v>
       </c>
+      <c r="F104" s="3">
+        <v>1</v>
+      </c>
+      <c r="G104" s="3"/>
       <c r="H104" s="6"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B105" s="3"/>
       <c r="D105" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E105" s="3">
         <v>1000</v>
@@ -2468,24 +2377,28 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B106" s="3"/>
       <c r="D106" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E106" s="3">
         <v>1000</v>
       </c>
       <c r="F106" s="3"/>
-      <c r="G106" s="3"/>
       <c r="H106" s="6"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B107" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C107" s="5">
+        <v>3.1</v>
+      </c>
       <c r="D107" s="8" t="s">
         <v>16</v>
       </c>
@@ -2494,13 +2407,18 @@
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
-      <c r="H107" s="6"/>
+      <c r="H107" s="5"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B108" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C108" s="5">
+        <v>2.7</v>
+      </c>
       <c r="D108" s="8" t="s">
         <v>16</v>
       </c>
@@ -2508,13 +2426,19 @@
         <v>1000</v>
       </c>
       <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
       <c r="H108" s="6"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B109" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C109" s="5">
+        <v>3.1</v>
+      </c>
       <c r="D109" s="8" t="s">
         <v>16</v>
       </c>
@@ -2523,11 +2447,11 @@
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3"/>
-      <c r="H109" s="5"/>
+      <c r="H109" s="6"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B110" s="3"/>
       <c r="D110" s="8" t="s">
@@ -2538,28 +2462,40 @@
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="3"/>
-      <c r="H110" s="6"/>
+      <c r="H110" s="4"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B111" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C111" s="5">
+        <v>2.5</v>
+      </c>
       <c r="D111" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E111" s="3">
         <v>1000</v>
       </c>
-      <c r="F111" s="3"/>
+      <c r="F111" s="3">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="G111" s="3"/>
       <c r="H111" s="6"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B112" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C112" s="5">
+        <v>2.4</v>
+      </c>
       <c r="D112" s="8" t="s">
         <v>16</v>
       </c>
@@ -2568,13 +2504,18 @@
       </c>
       <c r="F112" s="3"/>
       <c r="G112" s="3"/>
-      <c r="H112" s="4"/>
+      <c r="H112" s="6"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B113" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C113" s="5">
+        <v>3.9</v>
+      </c>
       <c r="D113" s="8" t="s">
         <v>16</v>
       </c>
@@ -2587,7 +2528,7 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B114" s="3"/>
       <c r="D114" s="8" t="s">
@@ -2598,11 +2539,11 @@
       </c>
       <c r="F114" s="3"/>
       <c r="G114" s="3"/>
-      <c r="H114" s="6"/>
+      <c r="H114" s="4"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B115" s="3"/>
       <c r="D115" s="8" t="s">
@@ -2611,72 +2552,77 @@
       <c r="E115" s="3">
         <v>1000</v>
       </c>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3"/>
       <c r="H115" s="6"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C116" s="5">
-        <v>7</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B116" s="3"/>
       <c r="D116" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E116" s="3">
         <v>1000</v>
       </c>
-      <c r="F116" s="3"/>
-      <c r="G116" s="3"/>
-      <c r="H116" s="4"/>
+      <c r="H116" s="6"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B117" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C117" s="5">
+        <v>2.6</v>
+      </c>
       <c r="D117" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E117" s="3">
         <v>1000</v>
       </c>
-      <c r="H117" s="6"/>
+      <c r="H117" s="4"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B118" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C118" s="5">
+        <v>3.9</v>
+      </c>
       <c r="D118" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E118" s="3">
         <v>1000</v>
       </c>
-      <c r="H118" s="6"/>
+      <c r="H118" s="4"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B119" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C119" s="5">
+        <v>1.9</v>
+      </c>
       <c r="D119" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E119" s="3">
         <v>1000</v>
       </c>
-      <c r="H119" s="4"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B120" s="3"/>
       <c r="D120" s="8" t="s">
@@ -2685,13 +2631,17 @@
       <c r="E120" s="3">
         <v>1000</v>
       </c>
-      <c r="H120" s="4"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B121" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C121" s="5">
+        <v>3.9</v>
+      </c>
       <c r="D121" s="8" t="s">
         <v>16</v>
       </c>
@@ -2701,36 +2651,40 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B122" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C122" s="5">
+        <v>5</v>
+      </c>
       <c r="D122" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E122" s="3">
         <v>1000</v>
       </c>
+      <c r="F122" s="3"/>
+      <c r="G122" s="3"/>
+      <c r="H122" s="3"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C123" s="5">
-        <v>1.3</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B123" s="3"/>
       <c r="D123" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E123" s="3">
         <v>1000</v>
       </c>
+      <c r="H123" s="6"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B124" s="3"/>
       <c r="D124" s="8" t="s">
@@ -2739,13 +2693,11 @@
       <c r="E124" s="3">
         <v>1000</v>
       </c>
-      <c r="F124" s="3"/>
-      <c r="G124" s="3"/>
-      <c r="H124" s="3"/>
+      <c r="H124" s="6"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B125" s="3"/>
       <c r="D125" s="8" t="s">
@@ -2754,13 +2706,18 @@
       <c r="E125" s="3">
         <v>1000</v>
       </c>
-      <c r="H125" s="6"/>
+      <c r="H125" s="9"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B126" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C126" s="5">
+        <v>2.4</v>
+      </c>
       <c r="D126" s="8" t="s">
         <v>16</v>
       </c>
@@ -2771,7 +2728,7 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B127" s="3"/>
       <c r="D127" s="8" t="s">
@@ -2780,11 +2737,11 @@
       <c r="E127" s="3">
         <v>1000</v>
       </c>
-      <c r="H127" s="9"/>
+      <c r="H127" s="4"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B128" s="3"/>
       <c r="D128" s="8" t="s">
@@ -2797,7 +2754,7 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B129" s="3"/>
       <c r="D129" s="8" t="s">
@@ -2806,11 +2763,11 @@
       <c r="E129" s="3">
         <v>1000</v>
       </c>
-      <c r="H129" s="4"/>
+      <c r="H129" s="6"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B130" s="3"/>
       <c r="D130" s="8" t="s">
@@ -2823,53 +2780,69 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B131" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C131" s="5">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="D131" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E131" s="3">
         <v>1000</v>
       </c>
-      <c r="H131" s="6"/>
+      <c r="F131">
+        <v>0.8</v>
+      </c>
+      <c r="H131" s="4"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B132" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C132" s="5">
+        <v>1.2</v>
+      </c>
       <c r="D132" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E132" s="3">
         <v>1000</v>
       </c>
+      <c r="F132">
+        <v>0.9</v>
+      </c>
       <c r="H132" s="6"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B133" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C133" s="5">
+        <v>2.6</v>
+      </c>
       <c r="D133" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E133" s="3">
         <v>1000</v>
       </c>
-      <c r="H133" s="4"/>
+      <c r="H133" s="6"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C134" s="5">
-        <v>5.6</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B134" s="3"/>
       <c r="D134" s="8" t="s">
         <v>16</v>
       </c>
@@ -2880,13 +2853,13 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C135" s="5">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="D135" s="8" t="s">
         <v>16</v>
@@ -2894,18 +2867,16 @@
       <c r="E135" s="3">
         <v>1000</v>
       </c>
+      <c r="F135">
+        <v>0.8</v>
+      </c>
       <c r="H135" s="6"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C136" s="5">
-        <v>3.1</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B136" s="3"/>
       <c r="D136" s="8" t="s">
         <v>16</v>
       </c>
@@ -2918,31 +2889,47 @@
       <c r="A137" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B137" s="3"/>
+      <c r="B137" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C137" s="5">
+        <v>1.4</v>
+      </c>
       <c r="D137" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E137" s="3">
         <v>1000</v>
       </c>
+      <c r="F137">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="H137" s="6"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B138" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C138" s="5">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="D138" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E138" s="3">
         <v>1000</v>
       </c>
+      <c r="F138">
+        <v>0.9</v>
+      </c>
       <c r="H138" s="6"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B139" s="3"/>
       <c r="D139" s="8" t="s">
@@ -2955,14 +2942,22 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B140" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C140" s="5">
+        <v>1</v>
+      </c>
       <c r="D140" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E140" s="3">
         <v>1000</v>
+      </c>
+      <c r="F140">
+        <v>0.8</v>
       </c>
       <c r="H140" s="6"/>
     </row>
@@ -2970,20 +2965,33 @@
       <c r="A141" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B141" s="3"/>
+      <c r="B141" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C141" s="5">
+        <v>1.6</v>
+      </c>
       <c r="D141" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E141" s="3">
         <v>1000</v>
       </c>
+      <c r="F141">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="H141" s="6"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B142" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C142" s="5">
+        <v>1.9</v>
+      </c>
       <c r="D142" s="8" t="s">
         <v>16</v>
       </c>
@@ -2994,13 +3002,13 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C143" s="5">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="D143" s="8" t="s">
         <v>16</v>
@@ -3008,36 +3016,31 @@
       <c r="E143" s="3">
         <v>1000</v>
       </c>
+      <c r="F143">
+        <v>1.3</v>
+      </c>
       <c r="H143" s="6"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B144" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C144" s="5">
-        <v>2.6</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B144" s="3"/>
       <c r="D144" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E144" s="3">
         <v>1000</v>
       </c>
-      <c r="H144" s="6"/>
+      <c r="F144" s="3"/>
+      <c r="G144" s="3"/>
+      <c r="H144" s="4"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B145" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C145" s="5">
-        <v>3.1</v>
-      </c>
+      <c r="B145" s="3"/>
       <c r="D145" s="8" t="s">
         <v>16</v>
       </c>
@@ -3048,7 +3051,7 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B146" s="3"/>
       <c r="D146" s="8" t="s">
@@ -3057,13 +3060,11 @@
       <c r="E146" s="3">
         <v>1000</v>
       </c>
-      <c r="F146" s="3"/>
-      <c r="G146" s="3"/>
-      <c r="H146" s="4"/>
+      <c r="H146" s="6"/>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B147" s="3"/>
       <c r="D147" s="8" t="s">
@@ -3076,7 +3077,7 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B148" s="3"/>
       <c r="D148" s="8" t="s">
@@ -3085,18 +3086,13 @@
       <c r="E148" s="3">
         <v>1000</v>
       </c>
-      <c r="H148" s="6"/>
+      <c r="H148" s="4"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C149" s="5">
-        <v>8.5</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B149" s="3"/>
       <c r="D149" s="8" t="s">
         <v>16</v>
       </c>
@@ -3107,7 +3103,7 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B150" s="3"/>
       <c r="D150" s="8" t="s">
@@ -3116,11 +3112,11 @@
       <c r="E150" s="3">
         <v>1000</v>
       </c>
-      <c r="H150" s="4"/>
+      <c r="H150" s="6"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B151" s="3"/>
       <c r="D151" s="8" t="s">
@@ -3133,7 +3129,7 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B152" s="3"/>
       <c r="D152" s="8" t="s">
@@ -3146,7 +3142,7 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B153" s="3"/>
       <c r="D153" s="8" t="s">
@@ -3159,7 +3155,7 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B154" s="3"/>
       <c r="D154" s="8" t="s">
@@ -3172,9 +3168,14 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B155" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="B155" t="s">
+        <v>12</v>
+      </c>
+      <c r="C155" s="5">
+        <v>1.6</v>
+      </c>
       <c r="D155" s="8" t="s">
         <v>16</v>
       </c>
@@ -3185,9 +3186,8 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B156" s="3"/>
+        <v>17</v>
+      </c>
       <c r="D156" s="8" t="s">
         <v>16</v>
       </c>
@@ -3198,20 +3198,22 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
-        <v>25</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B157" s="3"/>
       <c r="D157" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E157" s="3">
         <v>1000</v>
       </c>
-      <c r="H157" s="6"/>
+      <c r="H157" s="4"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
-        <v>26</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B158" s="3"/>
       <c r="D158" s="8" t="s">
         <v>16</v>
       </c>
@@ -3222,7 +3224,7 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B159" s="3"/>
       <c r="D159" s="8" t="s">
@@ -3231,36 +3233,27 @@
       <c r="E159" s="3">
         <v>1000</v>
       </c>
-      <c r="H159" s="4"/>
+      <c r="H159" s="6"/>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C160" s="5">
-        <v>1.9</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B160" s="3"/>
       <c r="D160" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E160" s="3">
         <v>1000</v>
       </c>
+      <c r="G160" s="3"/>
       <c r="H160" s="6"/>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C161" s="5">
-        <v>7.7</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B161" s="3"/>
       <c r="D161" s="8" t="s">
         <v>16</v>
       </c>
@@ -3271,7 +3264,7 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B162" s="3"/>
       <c r="D162" s="8" t="s">
@@ -3280,14 +3273,18 @@
       <c r="E162" s="3">
         <v>1000</v>
       </c>
-      <c r="G162" s="3"/>
       <c r="H162" s="6"/>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B163" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C163" s="5">
+        <v>3.9</v>
+      </c>
       <c r="D163" s="8" t="s">
         <v>16</v>
       </c>
@@ -3298,9 +3295,8 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B164" s="3"/>
+        <v>17</v>
+      </c>
       <c r="D164" s="8" t="s">
         <v>16</v>
       </c>
@@ -3311,9 +3307,8 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B165" s="3"/>
+        <v>17</v>
+      </c>
       <c r="D165" s="8" t="s">
         <v>16</v>
       </c>
@@ -3324,14 +3319,9 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>12</v>
-      </c>
-      <c r="C166" s="5">
-        <v>3.1</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B166" s="3"/>
       <c r="D166" s="8" t="s">
         <v>16</v>
       </c>
@@ -3342,8 +3332,9 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="3" t="s">
-        <v>25</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B167" s="3"/>
       <c r="D167" s="8" t="s">
         <v>16</v>
       </c>
@@ -3354,9 +3345,8 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B168" s="3"/>
+        <v>15</v>
+      </c>
       <c r="D168" s="8" t="s">
         <v>16</v>
       </c>
@@ -3367,9 +3357,8 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B169" s="3"/>
+        <v>17</v>
+      </c>
       <c r="D169" s="8" t="s">
         <v>16</v>
       </c>
@@ -3380,7 +3369,13 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="B170" t="s">
+        <v>12</v>
+      </c>
+      <c r="C170" s="5">
+        <v>4</v>
       </c>
       <c r="D170" s="8" t="s">
         <v>16</v>
@@ -3392,13 +3387,7 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B171" t="s">
-        <v>12</v>
-      </c>
-      <c r="C171" s="5">
-        <v>2.5</v>
+        <v>17</v>
       </c>
       <c r="D171" s="8" t="s">
         <v>16</v>
@@ -3410,7 +3399,7 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D172" s="8" t="s">
         <v>16</v>
@@ -3418,14 +3407,14 @@
       <c r="E172" s="3">
         <v>1000</v>
       </c>
-      <c r="H172" s="6"/>
+      <c r="H172" s="3"/>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E173" s="3">
         <v>1000</v>
@@ -3434,67 +3423,73 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E174" s="3">
         <v>1000</v>
       </c>
-      <c r="H174" s="3"/>
+      <c r="H174" s="6"/>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
+      </c>
+      <c r="B175" t="s">
+        <v>12</v>
+      </c>
+      <c r="C175" s="5">
+        <v>1.6</v>
       </c>
       <c r="D175" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E175" s="3">
         <v>1000</v>
       </c>
-      <c r="H175" s="6"/>
+      <c r="H175" s="3"/>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="B176" t="s">
+        <v>12</v>
+      </c>
+      <c r="C176" s="5">
+        <v>1</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E176" s="3">
         <v>1000</v>
+      </c>
+      <c r="F176">
+        <v>0.8</v>
       </c>
       <c r="H176" s="6"/>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B177" t="s">
-        <v>12</v>
-      </c>
-      <c r="C177" s="5">
-        <v>1.2</v>
+        <v>17</v>
       </c>
       <c r="D177" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E177" s="3">
         <v>1000</v>
       </c>
-      <c r="F177">
-        <v>1.2</v>
-      </c>
-      <c r="H177" s="3"/>
+      <c r="H177" s="6"/>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D178" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E178" s="3">
         <v>1000</v>
@@ -3503,10 +3498,10 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E179" s="3">
         <v>1000</v>
@@ -3515,72 +3510,57 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D180" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E180" s="3">
         <v>1000</v>
       </c>
-      <c r="H180" s="6"/>
+      <c r="H180" s="4"/>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E181" s="3">
         <v>1000</v>
       </c>
-      <c r="H181" s="6"/>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B182" t="s">
-        <v>12</v>
-      </c>
-      <c r="C182" s="5">
-        <v>1.1000000000000001</v>
+        <v>17</v>
       </c>
       <c r="D182" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E182" s="3">
         <v>1000</v>
       </c>
-      <c r="F182">
-        <v>0.8</v>
-      </c>
-      <c r="H182" s="4"/>
+      <c r="H182" s="6"/>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B183" t="s">
-        <v>12</v>
-      </c>
-      <c r="C183" s="5">
-        <v>1.9</v>
+        <v>15</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E183" s="3">
         <v>1000</v>
       </c>
+      <c r="H183" s="6"/>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E184" s="3">
         <v>1000</v>
@@ -3589,10 +3569,10 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E185" s="3">
         <v>1000</v>
@@ -3601,69 +3581,69 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D186" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E186" s="3">
         <v>1000</v>
       </c>
-      <c r="H186" s="6"/>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D187" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E187" s="3">
         <v>1000</v>
       </c>
-      <c r="H187" s="6"/>
+      <c r="H187" s="4"/>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D188" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E188" s="3">
         <v>1000</v>
       </c>
+      <c r="H188" s="4"/>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D189" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E189" s="3">
         <v>1000</v>
       </c>
-      <c r="H189" s="4"/>
+      <c r="H189" s="6"/>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D190" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E190" s="3">
         <v>1000</v>
       </c>
-      <c r="H190" s="4"/>
+      <c r="H190" s="6"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E191" s="3">
         <v>1000</v>
@@ -3672,52 +3652,58 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B192" t="s">
         <v>12</v>
       </c>
       <c r="C192" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D192" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E192" s="3">
         <v>1000</v>
+      </c>
+      <c r="F192">
+        <v>0.8</v>
       </c>
       <c r="H192" s="6"/>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B193" t="s">
         <v>12</v>
       </c>
       <c r="C193" s="5">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="D193" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E193" s="3">
         <v>1000</v>
+      </c>
+      <c r="F193">
+        <v>0.8</v>
       </c>
       <c r="H193" s="6"/>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B194" t="s">
         <v>12</v>
       </c>
       <c r="C194" s="5">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E194" s="3">
         <v>1000</v>
@@ -3726,10 +3712,10 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D195" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E195" s="3">
         <v>1000</v>
@@ -3738,10 +3724,10 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D196" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E196" s="3">
         <v>1000</v>
@@ -3750,49 +3736,58 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E197" s="3">
         <v>1000</v>
       </c>
-      <c r="H197" s="6"/>
+      <c r="H197" s="4"/>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B198" t="s">
-        <v>12</v>
-      </c>
-      <c r="C198" s="5">
-        <v>2.7</v>
+        <v>17</v>
       </c>
       <c r="D198" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E198" s="3">
         <v>1000</v>
       </c>
-      <c r="H198" s="6"/>
+      <c r="H198" s="4"/>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="B199" t="s">
+        <v>12</v>
+      </c>
+      <c r="C199" s="5">
+        <v>1.1000000000000001</v>
       </c>
       <c r="D199" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E199" s="3">
         <v>1000</v>
       </c>
-      <c r="H199" s="4"/>
+      <c r="F199">
+        <v>0.9</v>
+      </c>
+      <c r="H199" s="6"/>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="B200" t="s">
+        <v>12</v>
+      </c>
+      <c r="C200" s="5">
+        <v>1.2</v>
       </c>
       <c r="D200" s="8" t="s">
         <v>13</v>
@@ -3800,11 +3795,20 @@
       <c r="E200" s="3">
         <v>1000</v>
       </c>
-      <c r="H200" s="4"/>
+      <c r="F200">
+        <v>0.9</v>
+      </c>
+      <c r="H200" s="6"/>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="B201" t="s">
+        <v>12</v>
+      </c>
+      <c r="C201" s="5">
+        <v>1.1000000000000001</v>
       </c>
       <c r="D201" s="8" t="s">
         <v>13</v>
@@ -3812,17 +3816,29 @@
       <c r="E201" s="3">
         <v>1000</v>
       </c>
+      <c r="F201">
+        <v>0.7</v>
+      </c>
       <c r="H201" s="6"/>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="B202" t="s">
+        <v>12</v>
+      </c>
+      <c r="C202" s="5">
+        <v>1.1000000000000001</v>
       </c>
       <c r="D202" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E202" s="3">
         <v>1000</v>
+      </c>
+      <c r="F202">
+        <v>0.7</v>
       </c>
       <c r="H202" s="6"/>
     </row>
@@ -3830,12 +3846,6 @@
       <c r="A203" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B203" t="s">
-        <v>12</v>
-      </c>
-      <c r="C203" s="5">
-        <v>3.6</v>
-      </c>
       <c r="D203" s="8" t="s">
         <v>13</v>
       </c>
@@ -3846,7 +3856,13 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
+      </c>
+      <c r="B204" t="s">
+        <v>12</v>
+      </c>
+      <c r="C204" s="5">
+        <v>3.4</v>
       </c>
       <c r="D204" s="8" t="s">
         <v>13</v>
@@ -3858,7 +3874,7 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D205" s="8" t="s">
         <v>13</v>
@@ -3866,11 +3882,12 @@
       <c r="E205" s="3">
         <v>1000</v>
       </c>
-      <c r="H205" s="6"/>
+      <c r="G205" s="6"/>
+      <c r="H205" s="4"/>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D206" s="8" t="s">
         <v>13</v>
@@ -3878,17 +3895,12 @@
       <c r="E206" s="3">
         <v>1000</v>
       </c>
-      <c r="H206" s="6"/>
+      <c r="G206" s="6"/>
+      <c r="H206" s="4"/>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B207" t="s">
-        <v>12</v>
-      </c>
-      <c r="C207" s="5">
-        <v>1.2</v>
+        <v>17</v>
       </c>
       <c r="D207" s="8" t="s">
         <v>13</v>
@@ -3896,15 +3908,11 @@
       <c r="E207" s="3">
         <v>1000</v>
       </c>
-      <c r="F207">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="G207" s="6"/>
-      <c r="H207" s="4"/>
+      <c r="H207" s="6"/>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D208" s="8" t="s">
         <v>13</v>
@@ -3912,12 +3920,16 @@
       <c r="E208" s="3">
         <v>1000</v>
       </c>
-      <c r="G208" s="6"/>
-      <c r="H208" s="4"/>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="B209" t="s">
+        <v>12</v>
+      </c>
+      <c r="C209" s="5">
+        <v>1.5</v>
       </c>
       <c r="D209" s="8" t="s">
         <v>13</v>
@@ -3925,11 +3937,20 @@
       <c r="E209" s="3">
         <v>1000</v>
       </c>
+      <c r="F209">
+        <v>0.9</v>
+      </c>
       <c r="H209" s="6"/>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="3" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="B210" t="s">
+        <v>12</v>
+      </c>
+      <c r="C210" s="5">
+        <v>1.1000000000000001</v>
       </c>
       <c r="D210" s="8" t="s">
         <v>13</v>
@@ -3937,17 +3958,15 @@
       <c r="E210" s="3">
         <v>1000</v>
       </c>
+      <c r="F210">
+        <v>0.8</v>
+      </c>
+      <c r="H210" s="4"/>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B211" t="s">
-        <v>12</v>
-      </c>
-      <c r="C211" s="5">
-        <v>3.2</v>
-      </c>
       <c r="D211" s="8" t="s">
         <v>13</v>
       </c>
@@ -3958,7 +3977,7 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D212" s="8" t="s">
         <v>13</v>
@@ -3970,7 +3989,7 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D213" s="8" t="s">
         <v>13</v>
@@ -3982,7 +4001,7 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D214" s="8" t="s">
         <v>13</v>
@@ -3994,7 +4013,13 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="B215" t="s">
+        <v>12</v>
+      </c>
+      <c r="C215" s="5">
+        <v>1.2</v>
       </c>
       <c r="D215" s="8" t="s">
         <v>13</v>
@@ -4002,11 +4027,20 @@
       <c r="E215" s="3">
         <v>1000</v>
       </c>
+      <c r="F215">
+        <v>0.9</v>
+      </c>
       <c r="H215" s="6"/>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="B216" t="s">
+        <v>12</v>
+      </c>
+      <c r="C216" s="5">
+        <v>1.4</v>
       </c>
       <c r="D216" s="8" t="s">
         <v>13</v>
@@ -4014,11 +4048,14 @@
       <c r="E216" s="3">
         <v>1000</v>
       </c>
-      <c r="H216" s="4"/>
+      <c r="F216">
+        <v>1</v>
+      </c>
+      <c r="H216" s="6"/>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D217" s="8" t="s">
         <v>13</v>
@@ -4030,7 +4067,7 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D218" s="8" t="s">
         <v>13</v>
@@ -4042,7 +4079,7 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D219" s="8" t="s">
         <v>13</v>
@@ -4054,7 +4091,7 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D220" s="8" t="s">
         <v>13</v>
@@ -4066,13 +4103,13 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B221" t="s">
         <v>12</v>
       </c>
       <c r="C221" s="5">
-        <v>7.7</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D221" s="8" t="s">
         <v>13</v>
@@ -4080,17 +4117,20 @@
       <c r="E221" s="3">
         <v>1000</v>
       </c>
-      <c r="H221" s="6"/>
+      <c r="F221">
+        <v>0.5</v>
+      </c>
+      <c r="H221" s="4"/>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B222" t="s">
         <v>12</v>
       </c>
       <c r="C222" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D222" s="8" t="s">
         <v>13</v>
@@ -4098,11 +4138,20 @@
       <c r="E222" s="3">
         <v>1000</v>
       </c>
+      <c r="F222">
+        <v>0.5</v>
+      </c>
       <c r="H222" s="6"/>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="B223" t="s">
+        <v>12</v>
+      </c>
+      <c r="C223" s="5">
+        <v>1</v>
       </c>
       <c r="D223" s="8" t="s">
         <v>13</v>
@@ -4110,11 +4159,20 @@
       <c r="E223" s="3">
         <v>1000</v>
       </c>
-      <c r="H223" s="4"/>
+      <c r="F223">
+        <v>0.5</v>
+      </c>
+      <c r="H223" s="6"/>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="B224" t="s">
+        <v>12</v>
+      </c>
+      <c r="C224" s="5">
+        <v>0.9</v>
       </c>
       <c r="D224" s="8" t="s">
         <v>13</v>
@@ -4122,11 +4180,13 @@
       <c r="E224" s="3">
         <v>1000</v>
       </c>
-      <c r="H224" s="6"/>
+      <c r="F224">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="225" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A225" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D225" s="8" t="s">
         <v>13</v>
@@ -4134,17 +4194,10 @@
       <c r="E225" s="3">
         <v>1000</v>
       </c>
-      <c r="H225" s="6"/>
     </row>
     <row r="226" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A226" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B226" t="s">
-        <v>12</v>
-      </c>
-      <c r="C226" s="5">
-        <v>2.1</v>
+        <v>20</v>
       </c>
       <c r="D226" s="8" t="s">
         <v>13</v>
@@ -4155,7 +4208,7 @@
     </row>
     <row r="227" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A227" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D227" s="8" t="s">
         <v>13</v>
@@ -4166,7 +4219,7 @@
     </row>
     <row r="228" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A228" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D228" s="8" t="s">
         <v>13</v>
@@ -4174,10 +4227,11 @@
       <c r="E228" s="3">
         <v>1000</v>
       </c>
+      <c r="H228" s="6"/>
     </row>
     <row r="229" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A229" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D229" s="8" t="s">
         <v>13</v>
@@ -4188,7 +4242,7 @@
     </row>
     <row r="230" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A230" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D230" s="8" t="s">
         <v>13</v>
@@ -4197,10 +4251,11 @@
         <v>1000</v>
       </c>
       <c r="H230" s="6"/>
+      <c r="XFD230" s="6"/>
     </row>
     <row r="231" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A231" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D231" s="8" t="s">
         <v>13</v>
@@ -4208,10 +4263,11 @@
       <c r="E231" s="3">
         <v>1000</v>
       </c>
+      <c r="H231" s="4"/>
     </row>
     <row r="232" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A232" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D232" s="8" t="s">
         <v>13</v>
@@ -4220,11 +4276,10 @@
         <v>1000</v>
       </c>
       <c r="H232" s="6"/>
-      <c r="XFD232" s="6"/>
     </row>
     <row r="233" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A233" s="3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D233" s="8" t="s">
         <v>13</v>
@@ -4232,11 +4287,10 @@
       <c r="E233" s="3">
         <v>1000</v>
       </c>
-      <c r="H233" s="4"/>
     </row>
     <row r="234" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A234" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D234" s="8" t="s">
         <v>13</v>
@@ -4244,11 +4298,16 @@
       <c r="E234" s="3">
         <v>1000</v>
       </c>
-      <c r="H234" s="6"/>
     </row>
     <row r="235" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A235" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
+      </c>
+      <c r="B235" t="s">
+        <v>12</v>
+      </c>
+      <c r="C235" s="5">
+        <v>3.1</v>
       </c>
       <c r="D235" s="8" t="s">
         <v>13</v>
@@ -4256,10 +4315,11 @@
       <c r="E235" s="3">
         <v>1000</v>
       </c>
+      <c r="H235" s="4"/>
     </row>
     <row r="236" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A236" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D236" s="8" t="s">
         <v>13</v>
@@ -4270,7 +4330,13 @@
     </row>
     <row r="237" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A237" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="B237" t="s">
+        <v>12</v>
+      </c>
+      <c r="C237" s="5">
+        <v>1.5</v>
       </c>
       <c r="D237" s="8" t="s">
         <v>13</v>
@@ -4278,11 +4344,13 @@
       <c r="E237" s="3">
         <v>1000</v>
       </c>
-      <c r="H237" s="4"/>
+      <c r="F237">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="238" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A238" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D238" s="8" t="s">
         <v>13</v>
@@ -4293,7 +4361,7 @@
     </row>
     <row r="239" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A239" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D239" s="8" t="s">
         <v>13</v>
@@ -4301,10 +4369,11 @@
       <c r="E239" s="3">
         <v>1000</v>
       </c>
+      <c r="H239" s="6"/>
     </row>
     <row r="240" spans="1:8 16384:16384" x14ac:dyDescent="0.2">
       <c r="A240" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D240" s="8" t="s">
         <v>13</v>
@@ -4312,10 +4381,11 @@
       <c r="E240" s="3">
         <v>1000</v>
       </c>
+      <c r="H240" s="6"/>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D241" s="8" t="s">
         <v>13</v>
@@ -4323,11 +4393,11 @@
       <c r="E241" s="3">
         <v>1000</v>
       </c>
-      <c r="H241" s="6"/>
+      <c r="H241" s="4"/>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D242" s="8" t="s">
         <v>13</v>
@@ -4339,7 +4409,13 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="B243" t="s">
+        <v>12</v>
+      </c>
+      <c r="C243" s="5">
+        <v>1</v>
       </c>
       <c r="D243" s="8" t="s">
         <v>13</v>
@@ -4347,11 +4423,13 @@
       <c r="E243" s="3">
         <v>1000</v>
       </c>
-      <c r="H243" s="4"/>
+      <c r="F243">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D244" s="8" t="s">
         <v>13</v>
@@ -4359,11 +4437,16 @@
       <c r="E244" s="3">
         <v>1000</v>
       </c>
-      <c r="H244" s="6"/>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="B245" t="s">
+        <v>12</v>
+      </c>
+      <c r="C245" s="5">
+        <v>1.3</v>
       </c>
       <c r="D245" s="8" t="s">
         <v>13</v>
@@ -4371,16 +4454,14 @@
       <c r="E245" s="3">
         <v>1000</v>
       </c>
+      <c r="F245">
+        <v>0.8</v>
+      </c>
+      <c r="H245" s="6"/>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B246" t="s">
-        <v>12</v>
-      </c>
-      <c r="C246" s="5">
-        <v>0.8</v>
+        <v>17</v>
       </c>
       <c r="D246" s="8" t="s">
         <v>13</v>
@@ -4388,19 +4469,10 @@
       <c r="E246" s="3">
         <v>1000</v>
       </c>
-      <c r="F246">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B247" t="s">
-        <v>12</v>
-      </c>
-      <c r="C247" s="5">
-        <v>3.2</v>
+        <v>15</v>
       </c>
       <c r="D247" s="8" t="s">
         <v>13</v>
@@ -4408,17 +4480,16 @@
       <c r="E247" s="3">
         <v>1000</v>
       </c>
-      <c r="H247" s="6"/>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B248" t="s">
         <v>12</v>
       </c>
       <c r="C248" s="5">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="D248" s="8" t="s">
         <v>13</v>
@@ -4426,16 +4497,11 @@
       <c r="E248" s="3">
         <v>1000</v>
       </c>
+      <c r="H248" s="4"/>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B249" t="s">
-        <v>12</v>
-      </c>
-      <c r="C249" s="5">
-        <v>4.4000000000000004</v>
+        <v>15</v>
       </c>
       <c r="D249" s="8" t="s">
         <v>13</v>
@@ -4446,7 +4512,7 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D250" s="8" t="s">
         <v>13</v>
@@ -4454,11 +4520,10 @@
       <c r="E250" s="3">
         <v>1000</v>
       </c>
-      <c r="H250" s="4"/>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D251" s="8" t="s">
         <v>13</v>
@@ -4469,13 +4534,7 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B252" t="s">
-        <v>12</v>
-      </c>
-      <c r="C252" s="5">
-        <v>4.9000000000000004</v>
+        <v>15</v>
       </c>
       <c r="D252" s="8" t="s">
         <v>13</v>
@@ -4483,640 +4542,278 @@
       <c r="E252" s="3">
         <v>1000</v>
       </c>
+      <c r="H252" s="4"/>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A253" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D253" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E253" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A253" s="3"/>
+      <c r="D253" s="8"/>
+      <c r="E253" s="3"/>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A254" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D254" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E254" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H254" s="4"/>
+      <c r="A254" s="3"/>
+      <c r="D254" s="8"/>
+      <c r="E254" s="3"/>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A255" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D255" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E255" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A255" s="3"/>
+      <c r="D255" s="8"/>
+      <c r="E255" s="3"/>
+      <c r="H255" s="4"/>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A256" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D256" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E256" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A256" s="3"/>
+      <c r="D256" s="8"/>
+      <c r="E256" s="3"/>
+      <c r="H256" s="4"/>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A257" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D257" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E257" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H257" s="4"/>
+      <c r="A257" s="3"/>
+      <c r="D257" s="8"/>
+      <c r="E257" s="3"/>
+      <c r="H257" s="6"/>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A258" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D258" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E258" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H258" s="4"/>
+      <c r="A258" s="3"/>
+      <c r="D258" s="8"/>
+      <c r="E258" s="3"/>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A259" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B259" t="s">
-        <v>12</v>
-      </c>
-      <c r="C259" s="5">
-        <v>4.8</v>
-      </c>
-      <c r="D259" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E259" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H259" s="6"/>
+      <c r="A259" s="3"/>
+      <c r="D259" s="8"/>
+      <c r="E259" s="3"/>
+      <c r="H259" s="4"/>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A260" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B260" t="s">
-        <v>12</v>
-      </c>
-      <c r="C260" s="5">
-        <v>2.9</v>
-      </c>
-      <c r="D260" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E260" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A260" s="3"/>
+      <c r="D260" s="8"/>
+      <c r="E260" s="3"/>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A261" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D261" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E261" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H261" s="4"/>
+      <c r="A261" s="3"/>
+      <c r="D261" s="8"/>
+      <c r="E261" s="3"/>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A262" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B262" t="s">
-        <v>12</v>
-      </c>
-      <c r="C262" s="5">
-        <v>3.9</v>
-      </c>
-      <c r="D262" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E262" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A262" s="3"/>
+      <c r="D262" s="8"/>
+      <c r="E262" s="3"/>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A263" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D263" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E263" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A263" s="3"/>
+      <c r="D263" s="8"/>
+      <c r="E263" s="3"/>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A264" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D264" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E264" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A264" s="3"/>
+      <c r="D264" s="8"/>
+      <c r="E264" s="3"/>
+      <c r="H264" s="6"/>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A265" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B265" t="s">
-        <v>12</v>
-      </c>
-      <c r="C265" s="5">
-        <v>2.8</v>
-      </c>
-      <c r="D265" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E265" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A265" s="3"/>
+      <c r="D265" s="8"/>
+      <c r="E265" s="3"/>
+      <c r="H265" s="6"/>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A266" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D266" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E266" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A266" s="3"/>
+      <c r="D266" s="8"/>
+      <c r="E266" s="3"/>
       <c r="H266" s="6"/>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A267" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D267" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E267" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A267" s="3"/>
+      <c r="D267" s="8"/>
+      <c r="E267" s="3"/>
       <c r="H267" s="6"/>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A268" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D268" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E268" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H268" s="6"/>
+      <c r="A268" s="3"/>
+      <c r="D268" s="8"/>
+      <c r="E268" s="3"/>
+      <c r="H268" s="3"/>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A269" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D269" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E269" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H269" s="6"/>
+      <c r="A269" s="3"/>
+      <c r="D269" s="8"/>
+      <c r="E269" s="3"/>
+      <c r="H269" s="4"/>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A270" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D270" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E270" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H270" s="3"/>
+      <c r="A270" s="3"/>
+      <c r="D270" s="8"/>
+      <c r="E270" s="3"/>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A271" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D271" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E271" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H271" s="4"/>
+      <c r="A271" s="3"/>
+      <c r="D271" s="8"/>
+      <c r="E271" s="3"/>
+      <c r="H271" s="3"/>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A272" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B272" t="s">
-        <v>12</v>
-      </c>
-      <c r="C272" s="5">
-        <v>3.3</v>
-      </c>
-      <c r="D272" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E272" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A272" s="3"/>
+      <c r="D272" s="8"/>
+      <c r="E272" s="3"/>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A273" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B273" t="s">
-        <v>12</v>
-      </c>
-      <c r="C273" s="5">
-        <v>3.3</v>
-      </c>
-      <c r="D273" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E273" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H273" s="3"/>
+      <c r="A273" s="3"/>
+      <c r="D273" s="8"/>
+      <c r="E273" s="3"/>
+      <c r="H273" s="4"/>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A274" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B274" t="s">
-        <v>12</v>
-      </c>
-      <c r="C274" s="5">
-        <v>3.3</v>
-      </c>
-      <c r="D274" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E274" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A274" s="3"/>
+      <c r="D274" s="8"/>
+      <c r="E274" s="3"/>
+      <c r="H274" s="4"/>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A275" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B275" t="s">
-        <v>12</v>
-      </c>
-      <c r="C275" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D275" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E275" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F275">
-        <v>0.8</v>
-      </c>
+      <c r="A275" s="3"/>
+      <c r="D275" s="8"/>
+      <c r="E275" s="3"/>
       <c r="H275" s="4"/>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A276" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D276" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E276" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H276" s="4"/>
+      <c r="A276" s="3"/>
+      <c r="D276" s="8"/>
+      <c r="E276" s="3"/>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A277" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D277" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E277" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H277" s="4"/>
+      <c r="A277" s="3"/>
+      <c r="D277" s="8"/>
+      <c r="E277" s="3"/>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A278" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D278" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E278" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A278" s="3"/>
+      <c r="D278" s="8"/>
+      <c r="E278" s="3"/>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A279" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D279" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E279" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A279" s="3"/>
+      <c r="D279" s="8"/>
+      <c r="E279" s="3"/>
+      <c r="H279" s="6"/>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A280" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B280" t="s">
-        <v>12</v>
-      </c>
-      <c r="C280" s="5">
-        <v>1.6</v>
-      </c>
-      <c r="D280" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E280" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A280" s="3"/>
+      <c r="D280" s="8"/>
+      <c r="E280" s="3"/>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A281" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D281" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E281" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H281" s="6"/>
+      <c r="A281" s="3"/>
+      <c r="D281" s="8"/>
+      <c r="E281" s="3"/>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A282" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D282" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E282" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A282" s="3"/>
+      <c r="D282" s="8"/>
+      <c r="E282" s="3"/>
+      <c r="H282" s="4"/>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A283" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D283" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E283" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A283" s="3"/>
+      <c r="D283" s="8"/>
+      <c r="E283" s="3"/>
+      <c r="H283" s="6"/>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A284" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B284" t="s">
-        <v>12</v>
-      </c>
-      <c r="C284" s="5">
-        <v>2.9</v>
-      </c>
-      <c r="D284" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E284" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H284" s="4"/>
+      <c r="A284" s="3"/>
+      <c r="D284" s="8"/>
+      <c r="E284" s="3"/>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A285" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D285" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E285" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H285" s="6"/>
+      <c r="A285" s="3"/>
+      <c r="D285" s="8"/>
+      <c r="E285" s="3"/>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A286" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D286" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E286" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A286" s="3"/>
+      <c r="D286" s="8"/>
+      <c r="E286" s="3"/>
+      <c r="H286" s="4"/>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A287" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D287" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E287" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A287" s="3"/>
+      <c r="D287" s="8"/>
+      <c r="E287" s="3"/>
+      <c r="H287" s="6"/>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A288" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D288" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E288" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H288" s="4"/>
+      <c r="A288" s="3"/>
+      <c r="D288" s="8"/>
+      <c r="E288" s="3"/>
+      <c r="H288" s="6"/>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A289" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D289" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E289" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H289" s="6"/>
+      <c r="A289" s="3"/>
+      <c r="D289" s="8"/>
+      <c r="E289" s="3"/>
+      <c r="H289" s="4"/>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A290" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D290" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E290" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H290" s="6"/>
+      <c r="A290" s="3"/>
+      <c r="D290" s="8"/>
+      <c r="E290" s="3"/>
+      <c r="H290" s="4"/>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A291" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D291" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E291" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H291" s="4"/>
+      <c r="A291" s="4"/>
+      <c r="D291" s="8"/>
+      <c r="E291" s="3"/>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A292" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D292" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E292" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H292" s="4"/>
+      <c r="A292" s="4"/>
+      <c r="D292" s="8"/>
+      <c r="E292" s="3"/>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A293" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D293" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E293" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A293" s="4"/>
+      <c r="D293" s="8"/>
+      <c r="E293" s="3"/>
+      <c r="H293" s="6"/>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A294" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D294" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E294" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A294" s="4"/>
+      <c r="D294" s="8"/>
+      <c r="E294" s="3"/>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A295" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D295" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E295" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H295" s="6"/>
+      <c r="A295" s="4"/>
+      <c r="D295" s="8"/>
+      <c r="E295" s="3"/>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A296" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D296" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E296" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A296" s="4"/>
+      <c r="D296" s="8"/>
+      <c r="E296" s="3"/>
+      <c r="H296" s="6"/>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A297" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D297" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E297" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A297" s="4"/>
+      <c r="D297" s="8"/>
+      <c r="E297" s="3"/>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A298" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D298" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E298" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H298" s="6"/>
+      <c r="A298" s="4"/>
+      <c r="D298" s="8"/>
+      <c r="E298" s="3"/>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A299" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B299" t="s">
-        <v>12</v>
-      </c>
-      <c r="C299" s="5">
-        <v>2.8</v>
-      </c>
-      <c r="D299" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E299" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A299" s="4"/>
+      <c r="D299" s="8"/>
+      <c r="E299" s="3"/>
+      <c r="H299" s="4"/>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A300" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D300" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E300" s="3">
-        <v>1000</v>
-      </c>
+      <c r="A300" s="4"/>
+      <c r="D300" s="8"/>
+      <c r="E300" s="3"/>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A301" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D301" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E301" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H301" s="4"/>
+      <c r="A301" s="4"/>
+      <c r="D301" s="8"/>
+      <c r="E301" s="3"/>
+      <c r="H301" s="6"/>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A302" s="4"/>
@@ -5127,7 +4824,6 @@
       <c r="A303" s="4"/>
       <c r="D303" s="8"/>
       <c r="E303" s="3"/>
-      <c r="H303" s="6"/>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A304" s="4"/>
@@ -5173,6 +4869,7 @@
       <c r="A312" s="4"/>
       <c r="D312" s="8"/>
       <c r="E312" s="3"/>
+      <c r="H312" s="3"/>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A313" s="4"/>
@@ -5183,7 +4880,6 @@
       <c r="A314" s="4"/>
       <c r="D314" s="8"/>
       <c r="E314" s="3"/>
-      <c r="H314" s="3"/>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A315" s="4"/>
@@ -5224,6 +4920,7 @@
       <c r="A322" s="4"/>
       <c r="D322" s="8"/>
       <c r="E322" s="3"/>
+      <c r="H322" s="4"/>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A323" s="4"/>
@@ -5234,7 +4931,7 @@
       <c r="A324" s="4"/>
       <c r="D324" s="8"/>
       <c r="E324" s="3"/>
-      <c r="H324" s="4"/>
+      <c r="G324" s="4"/>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A325" s="4"/>
@@ -5325,6 +5022,7 @@
       <c r="A342" s="4"/>
       <c r="D342" s="8"/>
       <c r="E342" s="3"/>
+      <c r="H342" s="6"/>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" s="4"/>
@@ -5335,7 +5033,6 @@
       <c r="A344" s="4"/>
       <c r="D344" s="8"/>
       <c r="E344" s="3"/>
-      <c r="H344" s="6"/>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" s="4"/>
@@ -5546,6 +5243,7 @@
       <c r="A386" s="4"/>
       <c r="D386" s="8"/>
       <c r="E386" s="3"/>
+      <c r="H386" s="3"/>
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A387" s="4"/>
@@ -5556,7 +5254,6 @@
       <c r="A388" s="4"/>
       <c r="D388" s="8"/>
       <c r="E388" s="3"/>
-      <c r="H388" s="3"/>
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A389" s="4"/>
@@ -5582,6 +5279,7 @@
       <c r="A393" s="4"/>
       <c r="D393" s="8"/>
       <c r="E393" s="3"/>
+      <c r="H393" s="4"/>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A394" s="4"/>
@@ -5592,12 +5290,12 @@
       <c r="A395" s="4"/>
       <c r="D395" s="8"/>
       <c r="E395" s="3"/>
-      <c r="H395" s="4"/>
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A396" s="4"/>
       <c r="D396" s="8"/>
       <c r="E396" s="3"/>
+      <c r="H396" s="4"/>
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A397" s="4"/>
@@ -5608,7 +5306,6 @@
       <c r="A398" s="4"/>
       <c r="D398" s="8"/>
       <c r="E398" s="3"/>
-      <c r="H398" s="4"/>
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A399" s="4"/>
@@ -5619,6 +5316,7 @@
       <c r="A400" s="4"/>
       <c r="D400" s="8"/>
       <c r="E400" s="3"/>
+      <c r="H400" s="4"/>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A401" s="4"/>
@@ -5629,7 +5327,6 @@
       <c r="A402" s="4"/>
       <c r="D402" s="8"/>
       <c r="E402" s="3"/>
-      <c r="H402" s="4"/>
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A403" s="4"/>
@@ -5665,6 +5362,7 @@
       <c r="A409" s="4"/>
       <c r="D409" s="8"/>
       <c r="E409" s="3"/>
+      <c r="H409" s="4"/>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A410" s="4"/>
@@ -5675,7 +5373,6 @@
       <c r="A411" s="4"/>
       <c r="D411" s="8"/>
       <c r="E411" s="3"/>
-      <c r="H411" s="4"/>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A412" s="4"/>
@@ -5711,6 +5408,7 @@
       <c r="A418" s="4"/>
       <c r="D418" s="8"/>
       <c r="E418" s="3"/>
+      <c r="H418" s="4"/>
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A419" s="4"/>
@@ -5721,7 +5419,6 @@
       <c r="A420" s="4"/>
       <c r="D420" s="8"/>
       <c r="E420" s="3"/>
-      <c r="H420" s="4"/>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A421" s="4"/>
@@ -5747,6 +5444,7 @@
       <c r="A425" s="4"/>
       <c r="D425" s="8"/>
       <c r="E425" s="3"/>
+      <c r="H425" s="4"/>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A426" s="4"/>
@@ -5757,7 +5455,6 @@
       <c r="A427" s="4"/>
       <c r="D427" s="8"/>
       <c r="E427" s="3"/>
-      <c r="H427" s="4"/>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A428" s="4"/>
@@ -5808,28 +5505,29 @@
       <c r="A437" s="4"/>
       <c r="D437" s="8"/>
       <c r="E437" s="3"/>
+      <c r="H437" s="4"/>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A438" s="4"/>
       <c r="D438" s="8"/>
       <c r="E438" s="3"/>
+      <c r="H438" s="4"/>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A439" s="4"/>
       <c r="D439" s="8"/>
       <c r="E439" s="3"/>
-      <c r="H439" s="4"/>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A440" s="4"/>
       <c r="D440" s="8"/>
       <c r="E440" s="3"/>
-      <c r="H440" s="4"/>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A441" s="4"/>
       <c r="D441" s="8"/>
       <c r="E441" s="3"/>
+      <c r="H441" s="4"/>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A442" s="4"/>
@@ -5840,7 +5538,6 @@
       <c r="A443" s="4"/>
       <c r="D443" s="8"/>
       <c r="E443" s="3"/>
-      <c r="H443" s="4"/>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A444" s="4"/>
@@ -5881,6 +5578,7 @@
       <c r="A451" s="4"/>
       <c r="D451" s="8"/>
       <c r="E451" s="3"/>
+      <c r="F451" s="3"/>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A452" s="4"/>
@@ -5891,7 +5589,6 @@
       <c r="A453" s="4"/>
       <c r="D453" s="8"/>
       <c r="E453" s="3"/>
-      <c r="F453" s="3"/>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A454" s="4"/>
@@ -5952,6 +5649,7 @@
       <c r="A465" s="4"/>
       <c r="D465" s="8"/>
       <c r="E465" s="3"/>
+      <c r="H465" s="3"/>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A466" s="4"/>
@@ -5962,7 +5660,6 @@
       <c r="A467" s="4"/>
       <c r="D467" s="8"/>
       <c r="E467" s="3"/>
-      <c r="H467" s="3"/>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A468" s="4"/>
@@ -5988,6 +5685,7 @@
       <c r="A472" s="4"/>
       <c r="D472" s="8"/>
       <c r="E472" s="3"/>
+      <c r="H472" s="3"/>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A473" s="4"/>
@@ -5998,7 +5696,6 @@
       <c r="A474" s="4"/>
       <c r="D474" s="8"/>
       <c r="E474" s="3"/>
-      <c r="H474" s="3"/>
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A475" s="4"/>
@@ -6059,6 +5756,7 @@
       <c r="A486" s="4"/>
       <c r="D486" s="8"/>
       <c r="E486" s="3"/>
+      <c r="H486" s="4"/>
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A487" s="4"/>
@@ -6069,7 +5767,6 @@
       <c r="A488" s="4"/>
       <c r="D488" s="8"/>
       <c r="E488" s="3"/>
-      <c r="H488" s="4"/>
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A489" s="4"/>
@@ -6245,6 +5942,7 @@
       <c r="A523" s="4"/>
       <c r="D523" s="8"/>
       <c r="E523" s="3"/>
+      <c r="H523" s="4"/>
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A524" s="4"/>
@@ -6255,7 +5953,6 @@
       <c r="A525" s="4"/>
       <c r="D525" s="8"/>
       <c r="E525" s="3"/>
-      <c r="H525" s="4"/>
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A526" s="4"/>
@@ -6316,6 +6013,7 @@
       <c r="A537" s="4"/>
       <c r="D537" s="8"/>
       <c r="E537" s="3"/>
+      <c r="H537" s="4"/>
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A538" s="4"/>
@@ -6326,7 +6024,6 @@
       <c r="A539" s="4"/>
       <c r="D539" s="8"/>
       <c r="E539" s="3"/>
-      <c r="H539" s="4"/>
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A540" s="4"/>
@@ -6717,32 +6414,32 @@
       <c r="A617" s="4"/>
       <c r="D617" s="8"/>
       <c r="E617" s="3"/>
+      <c r="H617" s="4"/>
     </row>
     <row r="618" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A618" s="4"/>
       <c r="D618" s="8"/>
       <c r="E618" s="3"/>
+      <c r="H618" s="4"/>
     </row>
     <row r="619" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A619" s="4"/>
       <c r="D619" s="8"/>
       <c r="E619" s="3"/>
-      <c r="H619" s="4"/>
     </row>
     <row r="620" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A620" s="4"/>
       <c r="D620" s="8"/>
       <c r="E620" s="3"/>
-      <c r="H620" s="4"/>
     </row>
     <row r="621" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A621" s="4"/>
-      <c r="D621" s="8"/>
+      <c r="D621" s="3"/>
       <c r="E621" s="3"/>
     </row>
     <row r="622" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A622" s="4"/>
-      <c r="D622" s="8"/>
+      <c r="D622" s="3"/>
       <c r="E622" s="3"/>
     </row>
     <row r="623" spans="1:8" x14ac:dyDescent="0.2">
@@ -9271,12 +8968,10 @@
       <c r="E1127" s="3"/>
     </row>
     <row r="1128" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1128" s="4"/>
       <c r="D1128" s="3"/>
       <c r="E1128" s="3"/>
     </row>
     <row r="1129" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1129" s="4"/>
       <c r="D1129" s="3"/>
       <c r="E1129" s="3"/>
     </row>
@@ -9326,17 +9021,9 @@
     </row>
     <row r="1141" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D1141" s="3"/>
-      <c r="E1141" s="3"/>
-    </row>
-    <row r="1142" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D1142" s="3"/>
-      <c r="E1142" s="3"/>
-    </row>
-    <row r="1143" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D1143" s="3"/>
-    </row>
-    <row r="1048576" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H1048576" s="6"/>
+    </row>
+    <row r="1048574" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H1048574" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
